--- a/DB/company_data.xlsx
+++ b/DB/company_data.xlsx
@@ -105,78 +105,78 @@
   <si>
     <t>Apple Inc. designs, manufactures, and markets smartphones, personal computers, tablets, wearables, and accessories worldwide. The company offers iPhone, a line of smartphones; Mac, a line of personal computers; iPad, a line of multi-purpose tablets; and wearables, home, and accessories comprising AirPods, Apple TV, Apple Watch, Beats products, and HomePod. It also provides AppleCare support and cloud services; and operates various platforms, including the App Store that allow customers to discover and download applications and digital content, such as books, music, video, games, and podcasts, as well as advertising services include third-party licensing arrangements and its own advertising platforms. In addition, the company offers various subscription-based services, such as Apple Arcade, a game subscription service; Apple Fitness+, a personalized fitness service; Apple Music, which offers users a curated listening experience with on-demand radio stations; Apple News+, a subscription news and magazine service; Apple TV+, which offers exclusive original content; Apple Card, a co-branded credit card; and Apple Pay, a cashless payment service, as well as licenses its intellectual property. The company serves consumers, and small and mid-sized businesses; and the education, enterprise, and government markets. It distributes third-party applications for its products through the App Store. The company also sells its products through its retail and online stores, and direct sales force; and third-party cellular network carriers, wholesalers, retailers, and resellers. Apple Inc. was founded in 1976 and is headquartered in Cupertino, California.
 **Financial Metrics &amp; Fundamentals**
-- **Market Cap:** 3628287918080
-- **Total Revenues:** 391034994688
-- **Gross Profit Margin:** 0.46206
-- **EBITDA Margin:** 0.34437
-- **Operating Margin:** 0.31171
-- **Net Profit Margin:** 0.23971
-- **EPS Diluted:** 6.3
-- **P/E Ratio:** 38.338093
-- **Forward P/E Ratio:** 29.285307
+- **Market Cap:** 3674405863424
+- **Total Revenues:** 395760009216
+- **Gross Profit Margin:** 0.46519002
+- **EBITDA Margin:** 0.34706002
+- **Operating Margin:** 0.34459
+- **Net Profit Margin:** 0.24295
+- **EPS Diluted:** 6.31
+- **P/E Ratio:** 38.763866
+- **Forward P/E Ratio:** 29.662977
 **Recent News**
-- [Apple, Google Restore TikTok App After Assurances From Trump](https://finance.yahoo.com/m/2a8d943e-8717-3a19-a01f-2189b195381d/apple%2C-google-restore%C2%A0tiktok.html) (2025-02-14 01:20:05 UTC) (Bloomberg)
-- [Billionaire Ken Griffin sounds alarm on multinatonal stocks](https://finance.yahoo.com/m/a5c22ed2-94cf-3cce-b22e-d53d76e44074/billionaire-ken-griffin.html) (2025-02-14 00:03:00 UTC) (TheStreet)
-- [Steve Jobs Feared His Porsche 911 Would Display His Wealth And Cost Him A $20 Million Deal–So He Scrambled To Hide It From Ross Perot](https://finance.yahoo.com/news/steve-jobs-feared-porsche-911-213021341.html) (2025-02-13 21:30:21 UTC) (Benzinga)
-- [Is Apple Inc. (AAPL) the Best Major Stock to Buy According to Hedge Funds?](https://finance.yahoo.com/news/apple-inc-aapl-best-major-200250670.html) (2025-02-13 20:02:50 UTC) (Insider Monkey)
-- [Tim Cook teases Apple product news for February 19 -- likely the iPhone SE](https://finance.yahoo.com/m/312a2528-5a09-3c32-906b-ec302d6a9e23/tim-cook-teases-apple-product.html) (2025-02-13 19:23:24 UTC) (TechCrunch)
-- [Magnificent Seven Stocks: Nvidia Rallies Above Key Level; Tesla Extends Gains](https://finance.yahoo.com/m/4205eaa9-f620-3a0b-a81a-0e82c7c9fd0b/magnificent-seven-stocks%3A.html) (2025-02-13 19:20:42 UTC) (Investor's Business Daily)
-- [Apple CEO Tim Cook Hints at iPhone SE Launch, Stock Rises](https://finance.yahoo.com/news/apple-ceo-tim-cook-hints-191012799.html) (2025-02-13 19:10:12 UTC) (GuruFocus.com)
-- [Sector Update: Tech Stocks Gain Thursday Afternoon](https://finance.yahoo.com/news/sector-tech-stocks-gain-thursday-185630415.html) (2025-02-13 18:56:30 UTC) (MT Newswires)
+- [Is Apple Inc. (AAPL) the Most Profitable Tech Stock to Buy Now?](https://finance.yahoo.com/news/apple-inc-aapl-most-profitable-122451503.html) (2025-02-18 12:24:51 UTC) (Insider Monkey)
+- [Cloud AI Today - Check Point Leads AI Cybersecurity With CloudGuard Advancements](https://finance.yahoo.com/news/cloud-ai-today-check-point-120745016.html) (2025-02-18 12:07:45 UTC) (Simply Wall St.)
+- [Europe refuses to delay Meta and Apple antitrust decisions, despite pressure from the U.S.](https://finance.yahoo.com/m/3183603d-3400-39a0-8315-06b647fabd4f/europe-refuses-to-delay-meta.html) (2025-02-18 11:13:33 UTC) (Fortune)
+- [Is Apple Stock A Buy Before New Product Reveal?](https://finance.yahoo.com/m/8d01c248-e1eb-3b60-aba6-7725d3fcda1d/is-apple-stock-a-buy-before.html) (2025-02-18 11:00:38 UTC) (Investor's Business Daily)
+- [Warren Buffett's AI Bets: 24% of Berkshire Hathaway's $299 Billion Stock Portfolio Is in These 2 Artificial Intelligence Stocks](https://finance.yahoo.com/m/d6d44b83-f2b4-309d-8a3d-a545222a4913/warren-buffett%27s-ai-bets%3A-24%25.html) (2025-02-18 10:45:00 UTC) (Motley Fool)
+- [Should You Buy Apple Stock Hand Over Fist Before Feb. 19?](https://finance.yahoo.com/m/6111ff4a-1dcc-3fc2-a0e8-f9cd6cb34931/should-you-buy-apple-stock.html) (2025-02-18 10:15:00 UTC) (Motley Fool)
+- [Huawei's tri-foldable phone hits global markets in a show of defiance amid US curbs](https://finance.yahoo.com/m/1dfbb568-4f02-3460-9820-9e73c693e0c7/huawei%27s-tri-foldable-phone.html) (2025-02-18 09:56:32 UTC) (Associated Press Finance)
+- [The 3 Best Stocks to Buy and Hold for the Next Stage of the Artificial Intelligence (AI) Revolution](https://finance.yahoo.com/m/b2484ac2-2ca7-3a8b-893f-a7904fbd10e1/the-3-best-stocks-to-buy-and.html) (2025-02-18 09:15:00 UTC) (Motley Fool)
 **Stock Performance**
-- **Current Price:** 241.52999877929688
+- **Current Price:** 244.60000610351562
 - **52-Week Range:** 164.08 - 260.1
-- **YTD Total Return:** -0.84%
-- **1Y Total Return:** 31.14%
-- **5Y Total Return CAGR:** 42.28%
-- **10Y Total Return CAGR:** 74.60%
+- **YTD Total Return:** 0.42%
+- **1Y Total Return:** 33.45%
+- **5Y Total Return CAGR:** 41.61%
+- **10Y Total Return CAGR:** 75.68%
 **Summary**
 *Provide a brief summary of the company's performance and outlook.*</t>
   </si>
   <si>
-    <t>3628287918080</t>
-  </si>
-  <si>
-    <t>391034994688</t>
-  </si>
-  <si>
-    <t>0.46206</t>
-  </si>
-  <si>
-    <t>0.34437</t>
-  </si>
-  <si>
-    <t>0.31171</t>
-  </si>
-  <si>
-    <t>0.23971</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>38.338093</t>
-  </si>
-  <si>
-    <t>29.285307</t>
-  </si>
-  <si>
-    <t>241.52999877929688</t>
+    <t>3674405863424</t>
+  </si>
+  <si>
+    <t>395760009216</t>
+  </si>
+  <si>
+    <t>0.46519002</t>
+  </si>
+  <si>
+    <t>0.34706002</t>
+  </si>
+  <si>
+    <t>0.34459</t>
+  </si>
+  <si>
+    <t>0.24295</t>
+  </si>
+  <si>
+    <t>6.31</t>
+  </si>
+  <si>
+    <t>38.763866</t>
+  </si>
+  <si>
+    <t>29.662977</t>
+  </si>
+  <si>
+    <t>244.60000610351562</t>
   </si>
   <si>
     <t>164.08 - 260.1</t>
   </si>
   <si>
-    <t>-0.84%</t>
-  </si>
-  <si>
-    <t>31.14%</t>
-  </si>
-  <si>
-    <t>42.28%</t>
-  </si>
-  <si>
-    <t>74.60%</t>
+    <t>0.42%</t>
+  </si>
+  <si>
+    <t>33.45%</t>
+  </si>
+  <si>
+    <t>41.61%</t>
+  </si>
+  <si>
+    <t>75.68%</t>
   </si>
 </sst>
 </file>
